--- a/Sample Enrollement Record.xlsx
+++ b/Sample Enrollement Record.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anasa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addym\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B987A0A-1A3B-4DC0-B056-24ECA20F4B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E575932-23A9-48F5-8E6F-BFF19313077A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="10500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Enrollment" sheetId="1" r:id="rId1"/>
@@ -265,9 +265,6 @@
     <t>Student 32</t>
   </si>
   <si>
-    <t>UMN Global Identity</t>
-  </si>
-  <si>
     <t>Student 33</t>
   </si>
   <si>
@@ -728,6 +725,9 @@
   </si>
   <si>
     <t>Notes: Spanish classes are worth 5 credits and meet 30 minutes more that other classes</t>
+  </si>
+  <si>
+    <t>FOST 3352 UMN Global Identity</t>
   </si>
 </sst>
 </file>
@@ -2377,7 +2377,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="9"/>
       <c r="I34" s="13" t="s">
-        <v>76</v>
+        <v>230</v>
       </c>
       <c r="J34" s="18">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="35" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>60</v>
@@ -2412,7 +2412,7 @@
     </row>
     <row r="36" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>72</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="37" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>16</v>
@@ -2464,7 +2464,7 @@
     </row>
     <row r="38" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>37</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="39" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>21</v>
@@ -2511,7 +2511,7 @@
     </row>
     <row r="40" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>21</v>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="41" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>25</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="42" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>26</v>
@@ -2581,7 +2581,7 @@
     </row>
     <row r="43" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>24</v>
@@ -2605,7 +2605,7 @@
     </row>
     <row r="44" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>39</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="45" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>15</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="46" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>63</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="47" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>16</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="48" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>37</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="49" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>12</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>21</v>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>12</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>26</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>41</v>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>36</v>
@@ -2863,7 +2863,7 @@
     </row>
     <row r="55" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>36</v>
@@ -2887,7 +2887,7 @@
     </row>
     <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>60</v>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>42</v>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>26</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="59" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>29</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="60" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>21</v>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="61" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>60</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="62" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>29</v>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="63" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>29</v>
@@ -3096,7 +3096,7 @@
     </row>
     <row r="64" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>15</v>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="65" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>41</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="66" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>37</v>
@@ -3166,7 +3166,7 @@
     </row>
     <row r="67" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>45</v>
@@ -3189,7 +3189,7 @@
     </row>
     <row r="68" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>16</v>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="69" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>39</v>
@@ -3237,7 +3237,7 @@
     </row>
     <row r="70" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>31</v>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="71" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>36</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="72" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>24</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="73" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>35</v>
@@ -3338,7 +3338,7 @@
     </row>
     <row r="74" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>15</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="75" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>41</v>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="76" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>22</v>
@@ -3408,7 +3408,7 @@
     </row>
     <row r="77" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>37</v>
@@ -3432,7 +3432,7 @@
     </row>
     <row r="78" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>29</v>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="79" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>33</v>
@@ -6266,26 +6266,26 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="41"/>
       <c r="B1" s="41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B2" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>125</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -6302,7 +6302,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="49" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -6319,7 +6319,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -6336,7 +6336,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="49" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -6353,7 +6353,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -6370,7 +6370,7 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
@@ -6387,7 +6387,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -6438,45 +6438,45 @@
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
       <c r="D1" s="43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" s="42" t="s">
         <v>134</v>
-      </c>
-      <c r="E1" s="42" t="s">
-        <v>135</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="44" t="s">
+      <c r="C2" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="D2" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="E2" s="44" t="s">
         <v>139</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>140</v>
       </c>
       <c r="F2" s="45"/>
       <c r="G2" s="45"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="C3" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="D3" s="44" t="s">
         <v>143</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>144</v>
       </c>
       <c r="E3" s="44"/>
       <c r="F3" s="45"/>
@@ -6484,32 +6484,32 @@
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="C4" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="D4" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="E4" s="44" t="s">
         <v>148</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>149</v>
       </c>
       <c r="F4" s="45"/>
       <c r="G4" s="45"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="C5" s="44" t="s">
         <v>151</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>152</v>
       </c>
       <c r="D5" s="44"/>
       <c r="E5" s="46"/>
@@ -6518,13 +6518,13 @@
     </row>
     <row r="6" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="C6" s="44" t="s">
         <v>154</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>155</v>
       </c>
       <c r="D6" s="44"/>
       <c r="E6" s="44"/>
@@ -6533,13 +6533,13 @@
     </row>
     <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="C7" s="44" t="s">
         <v>157</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>158</v>
       </c>
       <c r="D7" s="44"/>
       <c r="E7" s="46"/>
@@ -6548,35 +6548,35 @@
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="C8" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="D8" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="E8" s="44" t="s">
         <v>162</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>163</v>
       </c>
       <c r="F8" s="45"/>
       <c r="G8" s="45"/>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="B9" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="C9" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="44" t="s">
         <v>165</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>166</v>
       </c>
       <c r="E9" s="44"/>
       <c r="F9" s="45"/>
@@ -6584,32 +6584,32 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="44" t="s">
-        <v>168</v>
-      </c>
       <c r="C10" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="E10" s="44" t="s">
         <v>162</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>163</v>
       </c>
       <c r="F10" s="45"/>
       <c r="G10" s="45"/>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="44" t="s">
         <v>169</v>
       </c>
-      <c r="B11" s="44" t="s">
+      <c r="C11" s="44" t="s">
         <v>170</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>171</v>
       </c>
       <c r="D11" s="44"/>
       <c r="E11" s="44"/>
@@ -6618,54 +6618,54 @@
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="B12" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B12" s="44" t="s">
-        <v>173</v>
-      </c>
       <c r="C12" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="E12" s="44" t="s">
         <v>162</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>163</v>
       </c>
       <c r="F12" s="45"/>
       <c r="G12" s="45"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="B13" s="44" t="s">
-        <v>175</v>
-      </c>
       <c r="C13" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="E13" s="44" t="s">
         <v>148</v>
-      </c>
-      <c r="E13" s="44" t="s">
-        <v>149</v>
       </c>
       <c r="F13" s="45"/>
       <c r="G13" s="45"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="C14" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="C14" s="44" t="s">
+      <c r="D14" s="44" t="s">
         <v>178</v>
-      </c>
-      <c r="D14" s="44" t="s">
-        <v>179</v>
       </c>
       <c r="E14" s="44"/>
       <c r="F14" s="45"/>
@@ -6673,16 +6673,16 @@
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="C15" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="D15" s="44" t="s">
         <v>182</v>
-      </c>
-      <c r="D15" s="44" t="s">
-        <v>183</v>
       </c>
       <c r="E15" s="46"/>
       <c r="F15" s="45"/>
@@ -6690,32 +6690,32 @@
     </row>
     <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="44" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="44" t="s">
         <v>184</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="C16" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="D16" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="D16" s="44" t="s">
+      <c r="E16" s="44" t="s">
         <v>187</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>188</v>
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="47"/>
     </row>
     <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="B17" s="44" t="s">
-        <v>190</v>
-      </c>
       <c r="C17" s="44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D17" s="44"/>
       <c r="E17" s="44"/>
@@ -6724,32 +6724,32 @@
     </row>
     <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="B18" s="44" t="s">
-        <v>192</v>
-      </c>
       <c r="C18" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="E18" s="44" t="s">
         <v>139</v>
-      </c>
-      <c r="E18" s="44" t="s">
-        <v>140</v>
       </c>
       <c r="F18" s="45"/>
       <c r="G18" s="45"/>
     </row>
     <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="B19" s="44" t="s">
-        <v>194</v>
-      </c>
       <c r="C19" s="44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D19" s="44"/>
       <c r="E19" s="44"/>
@@ -6758,13 +6758,13 @@
     </row>
     <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="B20" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="B20" s="44" t="s">
-        <v>196</v>
-      </c>
       <c r="C20" s="44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="44"/>
@@ -6773,13 +6773,13 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="B21" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="B21" s="44" t="s">
-        <v>198</v>
-      </c>
       <c r="C21" s="44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D21" s="44"/>
       <c r="E21" s="44"/>
@@ -6788,13 +6788,13 @@
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="B22" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="C22" s="44" t="s">
         <v>200</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>201</v>
       </c>
       <c r="D22" s="44"/>
       <c r="E22" s="44"/>
@@ -6803,13 +6803,13 @@
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="C23" s="44" t="s">
         <v>203</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>204</v>
       </c>
       <c r="D23" s="44"/>
       <c r="E23" s="46"/>
@@ -6818,13 +6818,13 @@
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="C24" s="44" t="s">
         <v>206</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>207</v>
       </c>
       <c r="D24" s="44"/>
       <c r="E24" s="44"/>
@@ -6833,16 +6833,16 @@
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="B25" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="B25" s="44" t="s">
+      <c r="C25" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="D25" s="44" t="s">
         <v>210</v>
-      </c>
-      <c r="D25" s="44" t="s">
-        <v>211</v>
       </c>
       <c r="E25" s="44"/>
       <c r="F25" s="45"/>
@@ -6850,16 +6850,16 @@
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="B26" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="B26" s="44" t="s">
+      <c r="C26" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="C26" s="44" t="s">
+      <c r="D26" s="44" t="s">
         <v>214</v>
-      </c>
-      <c r="D26" s="44" t="s">
-        <v>215</v>
       </c>
       <c r="E26" s="46"/>
       <c r="F26" s="45"/>
@@ -6867,16 +6867,16 @@
     </row>
     <row r="27" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="B27" s="44" t="s">
-        <v>217</v>
-      </c>
       <c r="C27" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="D27" s="44" t="s">
         <v>210</v>
-      </c>
-      <c r="D27" s="44" t="s">
-        <v>211</v>
       </c>
       <c r="E27" s="44"/>
       <c r="F27" s="45"/>
@@ -6884,13 +6884,13 @@
     </row>
     <row r="28" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="B28" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="B28" s="44" t="s">
+      <c r="C28" s="44" t="s">
         <v>219</v>
-      </c>
-      <c r="C28" s="44" t="s">
-        <v>220</v>
       </c>
       <c r="D28" s="44"/>
       <c r="E28" s="46"/>
@@ -6899,16 +6899,16 @@
     </row>
     <row r="29" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29" s="44" t="s">
         <v>221</v>
       </c>
-      <c r="B29" s="44" t="s">
+      <c r="C29" s="44" t="s">
         <v>222</v>
       </c>
-      <c r="C29" s="44" t="s">
+      <c r="D29" s="44" t="s">
         <v>223</v>
-      </c>
-      <c r="D29" s="44" t="s">
-        <v>224</v>
       </c>
       <c r="E29" s="46"/>
       <c r="F29" s="45"/>
@@ -6916,13 +6916,13 @@
     </row>
     <row r="30" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="B30" s="44" t="s">
-        <v>226</v>
-      </c>
       <c r="C30" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D30" s="44"/>
       <c r="E30" s="46"/>
@@ -6931,13 +6931,13 @@
     </row>
     <row r="31" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" s="44" t="s">
         <v>227</v>
       </c>
-      <c r="B31" s="44" t="s">
+      <c r="C31" s="44" t="s">
         <v>228</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>229</v>
       </c>
       <c r="D31" s="44"/>
       <c r="E31" s="44"/>
@@ -6946,7 +6946,7 @@
     </row>
     <row r="34" spans="1:1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
